--- a/data/club_weekly.xlsx
+++ b/data/club_weekly.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,33 @@
         </is>
       </c>
       <c r="E2" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>클러스터</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025년 36주차</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>동아리 활동 예정</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-09-04 23:19:13</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>과학</t>
         </is>
